--- a/llm_pricing.xlsx
+++ b/llm_pricing.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与折扣政策" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeepSeek" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kimi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MiniMax" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qwen" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunyuan" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERNIE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doubao" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MiMo" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claude" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenAI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grok" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="说明与折扣政策" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="总表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GLM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DeepSeek" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kimi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MiniMax" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Qwen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Hunyuan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ERNIE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Doubao" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MiMo" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Claude" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Gemini" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="OpenAI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Grok" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>4.5折（qwen3.7-max 6折 / preview 无折扣）</t>
+          <t>4.5折（qwen3.7/3.8-max 6折 / preview 无折扣）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>¥</t>
+          <t>¥/百万tokens</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -5939,17 +5939,17 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>0.15/0.30</t>
+          <t>0.14/0.44</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>0.6/1.2</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>0.003/0.006</t>
+          <t>0.0028</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -5959,17 +5959,17 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>$0.075/$0.15</t>
+          <t>$0.07/$0.22</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>$0.3/$0.6</t>
+          <t>$0.14</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>0.66/1.32</t>
+          <t>0.435/1.32</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>1.98/3.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>0.022/0.044</t>
+          <t>0.003625</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>$0.33/$0.66</t>
+          <t>$0.2175/$0.66</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>$0.99/$1.98</t>
+          <t>$0.435</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>qwen3.7-max</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>按量计费(国际)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>¥3.6</t>
+          <t>¥7.2</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>¥10.8</t>
+          <t>¥21.6</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -7282,22 +7282,22 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>qwen3-max</t>
+          <t>qwen3.8-flash</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>代码, 推理, Agent, 中文</t>
+          <t>极速, 低成本, 长文本, 多模态</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -7307,17 +7307,17 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>2.50/10.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>10.00/40.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>命中折扣</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>¥1.125/¥4.5</t>
+          <t>¥0.36</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>¥4.5/¥18</t>
+          <t>¥1.215</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
@@ -7354,17 +7354,17 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>qwen3-plus</t>
+          <t>qwen3.7-max</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>均衡, 代码, 长文本, 低成本</t>
+          <t>代码, 推理, 多模态, 长文本, Agent</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(国际)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -7394,17 +7394,17 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>4.5折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>¥0.36</t>
+          <t>¥3.6</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>¥0.9</t>
+          <t>¥10.8</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -7426,22 +7426,22 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>qwen3-flash</t>
+          <t>qwen3-max</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 长文本</t>
+          <t>代码, 推理, Agent, 中文</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>2.50/10.00</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>10.00/40.00</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>¥0.1651</t>
+          <t>¥1.125/¥4.5</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>¥1.3212</t>
+          <t>¥4.5/¥18</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>qwen-long</t>
+          <t>qwen3-plus</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>长文本, 低成本, 文档理解</t>
+          <t>均衡, 代码, 长文本, 低成本</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>命中折扣</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>¥0.225</t>
+          <t>¥0.36</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>qwen-turbo</t>
+          <t>qwen3-flash</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 中文</t>
+          <t>极速, 低成本, 长文本</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.936</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>命中折扣</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>¥0.135</t>
+          <t>¥0.1651</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>¥0.27</t>
+          <t>¥1.3212</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -7642,22 +7642,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>qwen3-omni-flash</t>
+          <t>qwen-long</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>多模态, 语音</t>
+          <t>长文本, 低成本, 文档理解</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>按量计费(多模态)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>1.80文本/15.8音频</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>6.9/12.7/62.6</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>¥0.81文本/¥7.11音频</t>
+          <t>¥0.225</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>¥3.105/¥5.715/¥28.17</t>
+          <t>¥0.9</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -7709,17 +7709,17 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>腾讯混元 Hunyuan</t>
+          <t>阿里通义 Qwen</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Hy4 preview</t>
+          <t>qwen-turbo</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>推理, 多模态, 长文本, 中文</t>
+          <t>极速, 低成本, 中文</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -7729,42 +7729,42 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>960K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>64K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>6.5折</t>
+          <t>4.5折</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>¥3.9</t>
+          <t>¥0.135</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>¥11.7</t>
+          <t>¥0.27</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
@@ -7774,34 +7774,34 @@
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>腾讯云官方</t>
+          <t>阿里云百炼官方</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>腾讯混元 Hunyuan</t>
+          <t>阿里通义 Qwen</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Hy3</t>
+          <t>qwen3-omni-flash</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>中文, 均衡, 长文本</t>
+          <t>多模态, 语音</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(多模态)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -7811,32 +7811,32 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.80文本/15.8音频</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.9/12.7/62.6</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>6.5折</t>
+          <t>4.5折</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>¥0.65</t>
+          <t>¥0.81文本/¥7.11音频</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>¥2.6</t>
+          <t>¥3.105/¥5.715/¥28.17</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>腾讯云官方</t>
+          <t>阿里云百炼官方</t>
         </is>
       </c>
     </row>
@@ -7858,12 +7858,12 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Hy3 preview</t>
+          <t>Hy4 preview</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>中文, 长文本</t>
+          <t>推理, 多模态, 长文本, 中文</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -7873,27 +7873,27 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>960K</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64K</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>¥0.78</t>
+          <t>¥3.9</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>¥2.6</t>
+          <t>¥11.7</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>hunyuan-T1-latest</t>
+          <t>Hy3</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>推理, 数学, 中文</t>
+          <t>中文, 均衡, 长文本</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>hunyuan-turbos-latest</t>
+          <t>Hy3 preview</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 中文</t>
+          <t>中文, 长文本</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -8027,17 +8027,17 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>¥0.52</t>
+          <t>¥0.78</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>¥1.3</t>
+          <t>¥2.6</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>hunyuan-pro</t>
+          <t>hunyuan-T1-latest</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>中文, 长文本, 知识问答</t>
+          <t>推理, 数学, 中文</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -8089,22 +8089,22 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>¥19.5</t>
+          <t>¥0.65</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>¥65</t>
+          <t>¥2.6</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>hunyuan-standard-256k</t>
+          <t>hunyuan-turbos-latest</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>长文本, 中文</t>
+          <t>极速, 低成本, 中文</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>¥9.75</t>
+          <t>¥0.52</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>¥39</t>
+          <t>¥1.3</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>hunyuan-standard</t>
+          <t>hunyuan-pro</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>中文, 低成本</t>
+          <t>中文, 长文本, 知识问答</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>2K</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>¥2.925</t>
+          <t>¥19.5</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>¥3.25</t>
+          <t>¥65</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>hunyuan-lite</t>
+          <t>hunyuan-standard-256k</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>低成本, 中文</t>
+          <t>长文本, 中文</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>250K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥9.75</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥39</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
@@ -8357,17 +8357,17 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>百度文心 ERNIE</t>
+          <t>腾讯混元 Hunyuan</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>ERNIE 5.1</t>
+          <t>hunyuan-standard</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>中文, 知识问答, 推理</t>
+          <t>中文, 低成本</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8377,22 +8377,22 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>32K~128K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2K</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>4.00/6.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>18.00/22.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -8402,17 +8402,17 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>6.5折</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>¥3.6/¥5.4</t>
+          <t>¥2.925</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>¥16.2/¥19.8</t>
+          <t>¥3.25</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -8422,24 +8422,24 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>百度千帆官方</t>
+          <t>腾讯云官方</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>百度文心 ERNIE</t>
+          <t>腾讯混元 Hunyuan</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>ERNIE 5.0</t>
+          <t>hunyuan-lite</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>中文, 知识问答, 推理</t>
+          <t>低成本, 中文</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>32K~128K</t>
+          <t>250K</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -8459,32 +8459,32 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>6.00/10.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>24.00/40.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>6.5折</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>¥5.4/¥9</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>¥21.6/¥36</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>百度千帆官方</t>
+          <t>腾讯云官方</t>
         </is>
       </c>
     </row>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>ERNIE X1 Turbo</t>
+          <t>ERNIE 5.1</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>推理, 中文, 低成本</t>
+          <t>中文, 知识问答, 推理</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>32K~128K</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00/6.00</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>18.00/22.00</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>¥0.9</t>
+          <t>¥3.6/¥5.4</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>¥3.6</t>
+          <t>¥16.2/¥19.8</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>ERNIE X1</t>
+          <t>ERNIE 5.0</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>推理, 数学, 中文</t>
+          <t>中文, 知识问答, 推理</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>32K~128K</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>6.00/10.00</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>24.00/40.00</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>¥1.8</t>
+          <t>¥5.4/¥9</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>¥7.2</t>
+          <t>¥21.6/¥36</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
@@ -8650,22 +8650,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>ERNIE 4.5 Turbo VL</t>
+          <t>ERNIE X1 Turbo</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>多模态, 视觉, 中文</t>
+          <t>推理, 中文, 低成本</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>按量计费(多模态)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>32K~128K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -8675,17 +8675,17 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>¥2.7</t>
+          <t>¥0.9</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>¥8.1</t>
+          <t>¥3.6</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>ERNIE 4.5</t>
+          <t>ERNIE X1</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>中文, 知识问答</t>
+          <t>推理, 数学, 中文</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>8K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>¥3.6</t>
+          <t>¥1.8</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>¥14.4</t>
+          <t>¥7.2</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>ERNIE 4.5 Turbo</t>
+          <t>ERNIE 4.5 Turbo VL</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>低成本, 中文, 长文本</t>
+          <t>多模态, 视觉, 中文</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(多模态)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -8819,17 +8819,17 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>¥0.72</t>
+          <t>¥2.7</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>¥2.88</t>
+          <t>¥8.1</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>ERNIE 4.0</t>
+          <t>ERNIE 4.5</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>ERNIE 3.5</t>
+          <t>ERNIE 4.5 Turbo</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>中文, 低成本</t>
+          <t>低成本, 中文, 长文本</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>8K~128K</t>
+          <t>32K~128K</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>¥1.8</t>
+          <t>¥2.88</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>ERNIE Speed</t>
+          <t>ERNIE 4.0</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 中文</t>
+          <t>中文, 知识问答</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>8K</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -9055,12 +9055,12 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥3.6</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥14.4</t>
         </is>
       </c>
       <c r="M55" s="10" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>ERNIE Lite</t>
+          <t>ERNIE 3.5</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>低成本, 中文</t>
+          <t>中文, 低成本</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>8K~128K</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥0.72</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥1.8</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>ERNIE Tiny</t>
+          <t>ERNIE Speed</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>8K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -9221,17 +9221,17 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>字节豆包 Doubao</t>
+          <t>百度文心 ERNIE</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Doubao-seed-2.1-pro</t>
+          <t>ERNIE Lite</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>多模态, 推理, 长文本, 中文</t>
+          <t>低成本, 中文</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -9241,42 +9241,42 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>¥5.7</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>¥28.5</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -9286,24 +9286,24 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>火山引擎官方</t>
+          <t>百度千帆官方</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>字节豆包 Doubao</t>
+          <t>百度文心 ERNIE</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Doubao-seed-2.1-turbo</t>
+          <t>ERNIE Tiny</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>均衡, 多模态, 低成本</t>
+          <t>极速, 低成本, 中文</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -9313,42 +9313,42 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>8K</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>¥2.85</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>¥14.25</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="M59" s="10" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>火山引擎官方</t>
+          <t>百度千帆官方</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Doubao-seed-2.0-pro</t>
+          <t>Doubao-seed-2.1-pro</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>多模态, 长文本, 中文</t>
+          <t>多模态, 推理, 长文本, 中文</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -9390,17 +9390,17 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>¥3.04</t>
+          <t>¥5.7</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>¥15.2</t>
+          <t>¥28.5</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Doubao-seed-2.0-lite</t>
+          <t>Doubao-seed-2.1-turbo</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>低成本, 极速, 多模态</t>
+          <t>均衡, 多模态, 低成本</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -9462,22 +9462,22 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>0.60/1.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>3.60/10.80</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>¥0.57/¥1.71</t>
+          <t>¥2.85</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>¥3.42/¥10.26</t>
+          <t>¥14.25</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Doubao-seed-2.0-mini</t>
+          <t>Doubao-seed-2.0-pro</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>极速, 低成本</t>
+          <t>多模态, 长文本, 中文</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -9539,17 +9539,17 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>0.20/0.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>2.00/8.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>¥0.19/¥0.76</t>
+          <t>¥3.04</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>¥1.9/¥7.6</t>
+          <t>¥15.2</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -9586,42 +9586,42 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Doubao-1.5-pro-32k</t>
+          <t>Doubao-seed-2.0-lite</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>中文, 知识问答, 低成本</t>
+          <t>低成本, 极速, 多模态</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>按量计费(命中折扣)</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
           <t>128K</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>12K</t>
-        </is>
-      </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.60/1.80</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60/10.80</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>¥0.76</t>
+          <t>¥0.57/¥1.71</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr">
         <is>
-          <t>¥1.9</t>
+          <t>¥3.42/¥10.26</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -9658,17 +9658,17 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Doubao-1.5-pro-256k</t>
+          <t>Doubao-seed-2.0-mini</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>长文本, 中文</t>
+          <t>极速, 低成本</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -9678,22 +9678,22 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>16K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.20/0.80</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.00/8.00</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>¥0.76</t>
+          <t>¥0.19/¥0.76</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>¥1.9</t>
+          <t>¥1.9/¥7.6</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -9730,42 +9730,42 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Doubao-1.5-lite</t>
+          <t>Doubao-1.5-pro-32k</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 中文</t>
+          <t>中文, 知识问答, 低成本</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(命中折扣)</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12K</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>¥0.285</t>
+          <t>¥0.76</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
         <is>
-          <t>¥0.57</t>
+          <t>¥1.9</t>
         </is>
       </c>
       <c r="M65" s="10" t="inlineStr">
@@ -9797,17 +9797,17 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>小米 MiMo</t>
+          <t>字节豆包 Doubao</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>MiMo-V2.6-Pro(≤256K)</t>
+          <t>Doubao-1.5-pro-256k</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>推理, 代码, 开源</t>
+          <t>长文本, 中文</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -9817,42 +9817,42 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>16K</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>¥2.64</t>
+          <t>¥0.76</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>¥5.28</t>
+          <t>¥1.9</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -9862,24 +9862,24 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>mimo.mi.com 官方</t>
+          <t>火山引擎官方</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>小米 MiMo</t>
+          <t>字节豆包 Doubao</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>MiMo-V2.6-Pro(256K-1M)</t>
+          <t>Doubao-1.5-lite</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>推理, 代码, 长文本</t>
+          <t>极速, 低成本, 中文</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -9889,22 +9889,22 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -9914,17 +9914,17 @@
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
-          <t>¥5.28</t>
+          <t>¥0.285</t>
         </is>
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>¥10.56</t>
+          <t>¥0.57</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N67" s="10" t="inlineStr">
         <is>
-          <t>mimo.mi.com 官方</t>
+          <t>火山引擎官方</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>MiMo-V2.6-Pro-UltraSpeed</t>
+          <t>MiMo-V2.6-Pro(≤256K)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>代码, 极速</t>
+          <t>推理, 代码, 开源</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>¥26.4</t>
+          <t>¥2.64</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>¥52.8</t>
+          <t>¥5.28</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>MiMo-V2.6-Flash</t>
+          <t>MiMo-V2.6-Pro(256K-1M)</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>代码, 极速, 低成本</t>
+          <t>推理, 代码, 长文本</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -10043,17 +10043,17 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>¥0.88</t>
+          <t>¥5.28</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
-          <t>¥1.76</t>
+          <t>¥10.56</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr">
@@ -10090,22 +10090,22 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>MiMo-V2-Omni</t>
+          <t>MiMo-V2.6-Pro-UltraSpeed</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>多模态, 视觉, 语音</t>
+          <t>代码, 极速</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>按量计费(多模态)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>¥2.5872</t>
+          <t>¥26.4</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>¥12.936</t>
+          <t>¥52.8</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>MiMo-V2-Flash</t>
+          <t>MiMo-V2.6-Flash</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>推理, 极速, 低成本</t>
+          <t>代码, 极速, 低成本</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -10182,22 +10182,22 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>64K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="K71" s="9" t="inlineStr">
         <is>
-          <t>¥0.616</t>
+          <t>¥0.88</t>
         </is>
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>¥1.848</t>
+          <t>¥1.76</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr">
@@ -10234,42 +10234,42 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>MiMo-V2-TTS</t>
+          <t>MiMo-V2-Omni</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>多模态, 视觉, 语音</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(多模态)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>8K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>8K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥2.5872</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>¥12.936</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -10301,17 +10301,17 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Anthropic Claude</t>
+          <t>小米 MiMo</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Claude Opus 5</t>
+          <t>MiMo-V2-Flash</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>代码, Agent, 推理, 长任务</t>
+          <t>推理, 极速, 低成本</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -10321,69 +10321,69 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>64K</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>7.5折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>¥0.616</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>$18.75</t>
+          <t>¥1.848</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
-          <t>$/百万tokens</t>
+          <t>¥/百万tokens</t>
         </is>
       </c>
       <c r="N73" s="10" t="inlineStr">
         <is>
-          <t>Anthropic 官方</t>
+          <t>mimo.mi.com 官方</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Anthropic Claude</t>
+          <t>小米 MiMo</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5</t>
+          <t>MiMo-V2-TTS</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>均衡, 代码, Agent</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -10393,52 +10393,52 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>8K</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>8K</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>7.5折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>$1.5</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>$7.5</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>$/百万tokens</t>
+          <t>¥/百万tokens</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Anthropic 官方</t>
+          <t>mimo.mi.com 官方</t>
         </is>
       </c>
     </row>
@@ -10450,12 +10450,12 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Claude Haiku 4.5</t>
+          <t>Claude Opus 5</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 代码</t>
+          <t>代码, Agent, 推理, 长任务</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -10465,27 +10465,27 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>$0.75</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$18.75</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Claude Fable 5</t>
+          <t>Claude Sonnet 5</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>创意写作, 长文本</t>
+          <t>均衡, 代码, Agent</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -10547,17 +10547,17 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -10567,17 +10567,17 @@
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
+          <t>$1.5</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
           <t>$7.5</t>
         </is>
       </c>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>$37.5</t>
-        </is>
-      </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
@@ -10594,12 +10594,12 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Claude Mythos 5</t>
+          <t>Claude Haiku 4.5</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>推理, 代码, Agent</t>
+          <t>极速, 低成本, 代码</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -10609,27 +10609,27 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
@@ -10639,17 +10639,17 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>$7.5</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>$37.5</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N77" s="10" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>Claude Fable 5</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>代码, Agent, 推理</t>
+          <t>创意写作, 长文本</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -10686,17 +10686,17 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$7.5</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>$18.75</t>
+          <t>$37.5</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Claude Opus 4.7</t>
+          <t>Claude Mythos 5</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>代码, Agent, 推理</t>
+          <t>推理, 代码, Agent</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -10758,17 +10758,17 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$7.5</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>$18.75</t>
+          <t>$37.5</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>Claude Opus 4.8</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>均衡, 代码, Agent</t>
+          <t>代码, Agent, 推理</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -10835,17 +10835,17 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>$2.25</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>$11.25</t>
+          <t>$18.75</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.5</t>
+          <t>Claude Opus 4.7</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>代码, Agent, 均衡</t>
+          <t>代码, Agent, 推理</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>$2.25</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>$11.25</t>
+          <t>$18.75</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Claude Haiku 3.5</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>极速, 低成本</t>
+          <t>均衡, 代码, Agent</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -10979,17 +10979,17 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>$0.6</t>
+          <t>$2.25</t>
         </is>
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>$3</t>
+          <t>$11.25</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -11021,22 +11021,22 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Google Gemini</t>
+          <t>Anthropic Claude</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro</t>
+          <t>Claude Sonnet 4.5</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>多模态, 长文本, 推理, 视频理解</t>
+          <t>代码, Agent, 均衡</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -11046,119 +11046,119 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>2.00/4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>12.00/18.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>7折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>$1.4/$2.8</t>
+          <t>$2.25</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
         <is>
-          <t>$8.4/$12.6</t>
+          <t>$11.25</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>Google AI 官方</t>
+          <t>Anthropic 官方</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Google Gemini</t>
+          <t>Anthropic Claude</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Gemini 3 Pro</t>
+          <t>Claude Haiku 3.5</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>多模态, 长文本, 推理, 视频理解</t>
+          <t>极速, 低成本</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>2.00/4.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>12.00/18.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>7折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>$1.4/$2.8</t>
+          <t>$0.6</t>
         </is>
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>$8.4/$12.6</t>
+          <t>$3</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Google AI 官方</t>
+          <t>Anthropic 官方</t>
         </is>
       </c>
     </row>
@@ -11170,17 +11170,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>多模态, 极速, 低成本</t>
+          <t>多模态, 长文本, 推理, 视频理解</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>按量计费(限时)</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
@@ -11195,17 +11195,17 @@
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.00/4.00</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>12.00/18.00</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>$0.525</t>
+          <t>$1.4/$2.8</t>
         </is>
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>$2.625</t>
+          <t>$8.4/$12.6</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
@@ -11242,17 +11242,17 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash</t>
+          <t>Gemini 3 Pro</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>多模态, 极速, 低成本</t>
+          <t>多模态, 长文本, 推理, 视频理解</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>按量计费(限时)</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -11267,17 +11267,17 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.00/4.00</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>12.00/18.00</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>$0.525</t>
+          <t>$1.4/$2.8</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>$2.625</t>
+          <t>$8.4/$12.6</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -11386,17 +11386,17 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>多模态, 长文本, 均衡</t>
+          <t>多模态, 极速, 低成本</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(限时)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -11411,17 +11411,17 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>$1.05</t>
+          <t>$0.525</t>
         </is>
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>$6.3</t>
+          <t>$2.625</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash-Lite</t>
+          <t>Gemini 3.6 Flash</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 多模态</t>
+          <t>多模态, 极速, 低成本</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(限时)</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="K89" s="9" t="inlineStr">
         <is>
-          <t>$0.21</t>
+          <t>$0.525</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
-          <t>$1.75</t>
+          <t>$2.625</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
@@ -11530,17 +11530,17 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>多模态, 长文本, 推理, 代码</t>
+          <t>多模态, 长文本, 均衡</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -11555,17 +11555,17 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>1.25/2.50</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>10.00/15.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>0.125/0.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>$0.875/$1.75</t>
+          <t>$1.05</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>$7/$10.5</t>
+          <t>$6.3</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -11602,12 +11602,12 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash</t>
+          <t>Gemini 3.5 Flash-Lite</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>多模态, 均衡, 低成本</t>
+          <t>极速, 低成本, 多模态</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash-Lite</t>
+          <t>Gemini 2.5 Pro</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>极速, 低成本</t>
+          <t>多模态, 长文本, 推理, 代码</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -11699,17 +11699,17 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>1.25/2.50</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>10.00/15.00</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.125/0.25</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>$0.07</t>
+          <t>$0.875/$1.75</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$7/$10.5</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -11741,17 +11741,17 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google Gemini</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Gemini 2.5 Flash</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>代码, Agent, 推理, 多模态</t>
+          <t>多模态, 均衡, 低成本</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -11761,42 +11761,42 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>400K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>7.5折</t>
+          <t>7折</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr">
         <is>
-          <t>$0.9375</t>
+          <t>$0.21</t>
         </is>
       </c>
       <c r="L93" s="9" t="inlineStr">
         <is>
-          <t>$7.5</t>
+          <t>$1.75</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
@@ -11806,24 +11806,24 @@
       </c>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>OpenAI 官方</t>
+          <t>Google AI 官方</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google Gemini</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>GPT-5 mini</t>
+          <t>Gemini 2.5 Flash-Lite</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>均衡, 低成本, 代码</t>
+          <t>极速, 低成本</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -11833,42 +11833,42 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>400K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>7.5折</t>
+          <t>7折</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
-          <t>$0.1875</t>
+          <t>$0.07</t>
         </is>
       </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>$1.5</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>OpenAI 官方</t>
+          <t>Google AI 官方</t>
         </is>
       </c>
     </row>
@@ -11890,12 +11890,12 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>GPT-5 nano</t>
+          <t>GPT-5</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本</t>
+          <t>代码, Agent, 推理, 多模态</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -11915,17 +11915,17 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>$0.0375</t>
+          <t>$0.9375</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>$0.3</t>
+          <t>$7.5</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>GPT-4.1</t>
+          <t>GPT-5 mini</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>代码, 长文本, 指令遵循</t>
+          <t>均衡, 低成本, 代码</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -11977,27 +11977,27 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>400K</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
+          <t>$0.1875</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
           <t>$1.5</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>$6</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>GPT-4.1 mini</t>
+          <t>GPT-5 nano</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>代码, 长文本, 低成本</t>
+          <t>极速, 低成本</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -12049,27 +12049,27 @@
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>400K</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
+          <t>$0.0375</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
           <t>$0.3</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>$1.2</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>GPT-4.1 nano</t>
+          <t>GPT-4.1</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>极速, 低成本</t>
+          <t>代码, 长文本, 指令遵循</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -12131,17 +12131,17 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -12151,12 +12151,12 @@
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>$0.075</t>
+          <t>$1.5</t>
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>$0.3</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>GPT-4.1 mini</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>多模态, 语音</t>
+          <t>代码, 长文本, 低成本</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -12193,27 +12193,27 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>16K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
@@ -12223,12 +12223,12 @@
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
-          <t>$1.875</t>
+          <t>$0.3</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>$7.5</t>
+          <t>$1.2</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>GPT-4o mini</t>
+          <t>GPT-4.1 nano</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>多模态, 低成本, 极速</t>
+          <t>极速, 低成本</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -12265,27 +12265,27 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>128K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>16K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>$0.1125</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>$0.45</t>
+          <t>$0.3</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>GPT-4o</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>推理, 数学, 代码</t>
+          <t>多模态, 语音</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -12337,27 +12337,27 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>16K</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="K101" s="9" t="inlineStr">
         <is>
-          <t>$1.5</t>
+          <t>$1.875</t>
         </is>
       </c>
       <c r="L101" s="9" t="inlineStr">
         <is>
-          <t>$6</t>
+          <t>$7.5</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>o3-pro</t>
+          <t>GPT-4o mini</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>推理, 数学</t>
+          <t>多模态, 低成本, 极速</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -12409,27 +12409,27 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>128K</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16K</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
-          <t>$15</t>
+          <t>$0.1125</t>
         </is>
       </c>
       <c r="L102" s="9" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$0.45</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>o4-mini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>推理, 数学, 低成本</t>
+          <t>推理, 数学, 代码</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
-          <t>$0.825</t>
+          <t>$1.5</t>
         </is>
       </c>
       <c r="L103" s="9" t="inlineStr">
         <is>
-          <t>$3.3</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
@@ -12538,12 +12538,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>o1</t>
+          <t>o3-pro</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>推理, 数学, 代码</t>
+          <t>推理, 数学</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -12563,17 +12563,17 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
-          <t>$11.25</t>
+          <t>$15</t>
         </is>
       </c>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>$60</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -12605,62 +12605,62 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>xAI Grok</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>grok-4.7</t>
+          <t>o4-mini</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>推理, 代码, 实时检索</t>
+          <t>推理, 数学, 低成本</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>500K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>2.00/4.00</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>6.00/12.00</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>0.50/1.00</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>6.5折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr">
         <is>
-          <t>$1.3/$2.6</t>
+          <t>$0.825</t>
         </is>
       </c>
       <c r="L105" s="9" t="inlineStr">
         <is>
-          <t>$3.9/$7.8</t>
+          <t>$3.3</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
@@ -12670,34 +12670,34 @@
       </c>
       <c r="N105" s="10" t="inlineStr">
         <is>
-          <t>xAI 官方</t>
+          <t>OpenAI 官方</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>xAI Grok</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>grok-4.6</t>
+          <t>o1</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>推理, 代码, 实时检索</t>
+          <t>推理, 数学, 代码</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>500K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -12707,32 +12707,32 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>2.00/4.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>6.00/12.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>0.50/1.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>6.5折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>$1.3/$2.6</t>
+          <t>$11.25</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>$3.9/$7.8</t>
+          <t>$45</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
-          <t>xAI 官方</t>
+          <t>OpenAI 官方</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>grok-4.5</t>
+          <t>grok-4.7</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>0.30/0.60</t>
+          <t>0.50/1.00</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>grok-4.3</t>
+          <t>grok-4.6</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>推理, 代码, 实时检索, 长文本</t>
+          <t>推理, 代码, 实时检索</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>500K</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -12851,17 +12851,17 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>1.25/2.50</t>
+          <t>2.00/4.00</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>2.50/5.00</t>
+          <t>6.00/12.00</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>0.20/0.40</t>
+          <t>0.50/1.00</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -12871,12 +12871,12 @@
       </c>
       <c r="K108" s="9" t="inlineStr">
         <is>
-          <t>$0.8125/$1.625</t>
+          <t>$1.3/$2.6</t>
         </is>
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>$1.625/$3.25</t>
+          <t>$3.9/$7.8</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>grok-4.20-0309-reasoning</t>
+          <t>grok-4.5</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>推理, 数学, 代码</t>
+          <t>推理, 代码, 实时检索</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>500K</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -12923,17 +12923,17 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>1.25/2.50</t>
+          <t>2.00/4.00</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>2.50/5.00</t>
+          <t>6.00/12.00</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>0.20/0.40</t>
+          <t>0.30/0.60</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="K109" s="9" t="inlineStr">
         <is>
-          <t>$0.8125/$1.625</t>
+          <t>$1.3/$2.6</t>
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr">
         <is>
-          <t>$1.625/$3.25</t>
+          <t>$3.9/$7.8</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>grok-4.20-0309-non-reasoning</t>
+          <t>grok-4.3</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>通用, 极速</t>
+          <t>推理, 代码, 实时检索, 长文本</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>grok-4.20-0309-multi-agent</t>
+          <t>grok-4.20-0309-reasoning</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Agent, 多模态</t>
+          <t>推理, 数学, 代码</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -13114,65 +13114,209 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>通用, 极速</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>按量计费(阶梯)</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>1.25/2.50</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>2.50/5.00</t>
+        </is>
+      </c>
+      <c r="I112" s="7" t="inlineStr">
+        <is>
+          <t>0.20/0.40</t>
+        </is>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
+        <is>
+          <t>6.5折</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>$0.8125/$1.625</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>$1.625/$3.25</t>
+        </is>
+      </c>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>$/百万tokens</t>
+        </is>
+      </c>
+      <c r="N112" s="7" t="inlineStr">
+        <is>
+          <t>xAI 官方</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>xAI Grok</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-multi-agent</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Agent, 多模态</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>按量计费(阶梯)</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>1.25/2.50</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>2.50/5.00</t>
+        </is>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>0.20/0.40</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>6.5折</t>
+        </is>
+      </c>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>$0.8125/$1.625</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>$1.625/$3.25</t>
+        </is>
+      </c>
+      <c r="M113" s="10" t="inlineStr">
+        <is>
+          <t>$/百万tokens</t>
+        </is>
+      </c>
+      <c r="N113" s="10" t="inlineStr">
+        <is>
+          <t>xAI 官方</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>xAI Grok</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
           <t>grok-build-0.1</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>代码, Agent</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>按量计费(阶梯)</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>256K</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>1.00/2.00</t>
         </is>
       </c>
-      <c r="H112" s="7" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr">
         <is>
           <t>2.00/4.00</t>
         </is>
       </c>
-      <c r="I112" s="7" t="inlineStr">
+      <c r="I114" s="7" t="inlineStr">
         <is>
           <t>0.20/0.40</t>
         </is>
       </c>
-      <c r="J112" s="8" t="inlineStr">
+      <c r="J114" s="8" t="inlineStr">
         <is>
           <t>6.5折</t>
         </is>
       </c>
-      <c r="K112" s="9" t="inlineStr">
+      <c r="K114" s="9" t="inlineStr">
         <is>
           <t>$0.65/$1.3</t>
         </is>
       </c>
-      <c r="L112" s="9" t="inlineStr">
+      <c r="L114" s="9" t="inlineStr">
         <is>
           <t>$1.3/$2.6</t>
         </is>
       </c>
-      <c r="M112" s="7" t="inlineStr">
+      <c r="M114" s="7" t="inlineStr">
         <is>
           <t>$/百万tokens</t>
         </is>
       </c>
-      <c r="N112" s="7" t="inlineStr">
+      <c r="N114" s="7" t="inlineStr">
         <is>
           <t>xAI 官方</t>
         </is>
@@ -13446,7 +13590,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -13466,7 +13610,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>¥</t>
+          <t>¥/百万tokens</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -14068,17 +14212,17 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>0.15/0.30</t>
+          <t>0.14/0.44</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>0.6/1.2</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>0.003/0.006</t>
+          <t>0.0028</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -14088,17 +14232,17 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>$0.075/$0.15</t>
+          <t>$0.07/$0.22</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>$0.3/$0.6</t>
+          <t>$0.14</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -14135,17 +14279,17 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>0.66/1.32</t>
+          <t>0.435/1.32</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>1.98/3.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>0.022/0.044</t>
+          <t>0.003625</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -14155,17 +14299,17 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>$0.33/$0.66</t>
+          <t>$0.2175/$0.66</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>$0.99/$1.98</t>
+          <t>$0.435</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/百万tokens</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
@@ -15449,7 +15593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15537,7 +15681,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>qwen3.7-max</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -15547,7 +15691,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>按量计费(国际)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -15562,12 +15706,12 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -15582,12 +15726,12 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>¥3.6</t>
+          <t>¥7.2</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>¥10.8</t>
+          <t>¥21.6</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -15604,22 +15748,22 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>qwen3-max</t>
+          <t>qwen3.8-flash</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>代码, 推理, Agent, 中文</t>
+          <t>极速, 低成本, 长文本, 多模态</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>按量计费(阶梯)</t>
+          <t>按量计费</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -15629,17 +15773,17 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>2.50/10.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>10.00/40.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>命中折扣</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -15649,12 +15793,12 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>¥1.125/¥4.5</t>
+          <t>¥0.36</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>¥4.5/¥18</t>
+          <t>¥1.215</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
@@ -15671,17 +15815,17 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>qwen3-plus</t>
+          <t>qwen3.7-max</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>均衡, 代码, 长文本, 低成本</t>
+          <t>代码, 推理, 多模态, 长文本, Agent</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(国际)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -15696,12 +15840,12 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -15711,17 +15855,17 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>4.5折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>¥0.36</t>
+          <t>¥3.6</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>¥0.9</t>
+          <t>¥10.8</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -15738,22 +15882,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>qwen3-flash</t>
+          <t>qwen3-max</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 长文本</t>
+          <t>代码, 推理, Agent, 中文</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>按量计费</t>
+          <t>按量计费(阶梯)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -15763,12 +15907,12 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>2.50/10.00</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>10.00/40.00</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -15783,12 +15927,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>¥0.1651</t>
+          <t>¥1.125/¥4.5</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>¥1.3212</t>
+          <t>¥4.5/¥18</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
@@ -15805,12 +15949,12 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>qwen-long</t>
+          <t>qwen3-plus</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>长文本, 低成本, 文档理解</t>
+          <t>均衡, 代码, 长文本, 低成本</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -15830,7 +15974,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -15840,7 +15984,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>命中折扣</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -15850,7 +15994,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>¥0.225</t>
+          <t>¥0.36</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -15872,12 +16016,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>qwen-turbo</t>
+          <t>qwen3-flash</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>极速, 低成本, 中文</t>
+          <t>极速, 低成本, 长文本</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -15897,17 +16041,17 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.936</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>命中折扣</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -15917,12 +16061,12 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>¥0.135</t>
+          <t>¥0.1651</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>¥0.27</t>
+          <t>¥1.3212</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
@@ -15939,65 +16083,199 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>qwen-long</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>长文本, 低成本, 文档理解</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>按量计费</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>4.5折</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>¥0.225</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>¥0.9</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>¥/百万tokens</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>阿里云百炼官方</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>qwen-turbo</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>极速, 低成本, 中文</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>按量计费</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>4.5折</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>¥0.135</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>¥0.27</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>¥/百万tokens</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>阿里云百炼官方</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>qwen3-omni-flash</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>多模态, 语音</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>按量计费(多模态)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>1.80文本/15.8音频</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>6.9/12.7/62.6</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>4.5折</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>¥0.81文本/¥7.11音频</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>¥3.105/¥5.715/¥28.17</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>¥/百万tokens</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>阿里云百炼官方</t>
         </is>

--- a/llm_pricing.xlsx
+++ b/llm_pricing.xlsx
@@ -525,7 +525,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>国内外主流大模型 API 定价对比（含代理折扣）</t>
+          <t>国内外主流大模型 API 定价对比（含折扣）</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>¥7.2</t>
+          <t>¥10.2</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>¥21.6</t>
+          <t>¥30.6</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>4.5折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>¥0.36</t>
+          <t>¥0.68</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>¥1.215</t>
+          <t>¥2.295</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
@@ -15721,17 +15721,17 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>¥7.2</t>
+          <t>¥10.2</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>¥21.6</t>
+          <t>¥30.6</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -15788,17 +15788,17 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>4.5折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>¥0.36</t>
+          <t>¥0.68</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>¥1.215</t>
+          <t>¥2.295</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
